--- a/config/card_battle_recommend.xlsx
+++ b/config/card_battle_recommend.xlsx
@@ -2157,7 +2157,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>炎と会心</t>
+          <t>火焰与会心</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>炎と会心</t>
+          <t>火焰与会心</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>炎と会心</t>
+          <t>火焰与会心</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>火属性で高い会心率とダメージを与え、火傷を付与する編成</t>
+          <t>以火属性给予高暴击率和伤害，并给予烧伤的编成</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>火傷効果</t>
+          <t>烧伤效果</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AH4" s="4" t="inlineStr">
         <is>
-          <t>火傷を付与された敵は各ターン開始時にダメージを負う(火傷は最大5層まで重複可能)</t>
+          <t>被赋予烧伤的敌人在各回合开始时受到伤害（烧伤最多可重复5层）</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AM4" s="6" t="inlineStr">
         <is>
-          <t>1、火焰鳥：パッシブスキルは炎属性の光輪を発動する。チーム全体の会心ダメージが上昇し、アクティブスキルは全体に火傷効果を付与して、全体の会心率を上昇する。</t>
+          <t>1、火焰鸟：被动技能发动炎属性的光轮。队伍全体的暴击伤害上升，主动技能给予全体的烧伤效果，使全体的暴击率上升。</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AR4" s="6" t="inlineStr">
         <is>
-          <t>2.炎帝：炎属性の前列シールド、パッシブスキル火神庇護が生存率を保証、自身のHPを失うが高い効果を獲得する。炎属性の必殺スキルは発動が遅いため、時間稼ぎを付与する。</t>
+          <t>2.炎帝：炎属性的前排护盾，被动技能火神庇护能保证生存率，自身的生命值会失去很高的效果。由于炎属性的必杀技能发动缓慢，给予时间争取。</t>
         </is>
       </c>
       <c r="AS4" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AW4" s="6" t="inlineStr">
         <is>
-          <t>3.鴨嘴寶寶：全スキルに火傷効果が付与され、目標に付与された全ての火傷効果を発動し、大ダメージを与える。</t>
+          <t>3.鸭嘴宝宝：所有技能都被赋予烧伤效果，发动所有被赋予目标的烧伤效果，造成巨大伤害。</t>
         </is>
       </c>
       <c r="AX4" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="BB4" s="6" t="inlineStr">
         <is>
-          <t>4.火焰雞：敵1体に大ダメージを与え、火傷状態の目標にさらに高いダメージを与える。</t>
+          <t>4.火焰鸡：对1个敌人造成巨大伤害，对处于烧伤状态的目标造成更高伤害。</t>
         </is>
       </c>
       <c r="BC4" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="BG4" s="6" t="inlineStr">
         <is>
-          <t>5.風速狗：火属性チームの高速アタッカー。先手を取り、瞬時に敵を戦闘不能にする。</t>
+          <t>风速狗：火属性队伍的高速攻击者。先下手为强，瞬间使敌人无法战斗。</t>
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="BL4" s="6" t="inlineStr">
         <is>
-          <t>6.黑魯加：仲間に攻撃バフを付与する。</t>
+          <t>6.黑鲁加：给予伙伴攻击增益。</t>
         </is>
       </c>
       <c r="BM4" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>速度重視</t>
+          <t>重视速度</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>速度重視</t>
+          <t>重视速度</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>速度重視</t>
+          <t>重视速度</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>敵より先に行動し、秒殺することで、敵を圧倒する編成</t>
+          <t>比敌人先行动，通过秒杀来压倒敌人的编成</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>速度重視</t>
+          <t>重视速度</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AH5" s="4" t="inlineStr">
         <is>
-          <t>会心耐性と速度上昇、さらにデバフ解除もある編成</t>
+          <t>暴击抵抗和速度上升，还有减益解除的编成</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AM5" s="6" t="inlineStr">
         <is>
-          <t>1、：チーム全体に速度光輪と会心耐性能力を発動する。必殺スキルはデバフ効果を解除し、会心ダメージを減少する。</t>
+          <t>1、对整个队伍发动速度光轮和暴击抵抗。必杀技能解除减益效果，减少暴击伤害。</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AR5" s="6" t="inlineStr">
         <is>
-          <t>2.甲贺忍蛙、暴鲤龙、水属性内の最強のアタッカー</t>
+          <t>甲贺忍蛙、暴鲤龙、水属性内最强的攻击者</t>
         </is>
       </c>
       <c r="AS5" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AW5" s="6" t="inlineStr">
         <is>
-          <t>3.巨沼怪：水属性チームのタンク役となる。</t>
+          <t>3.巨沼怪：水属性队伍的坦克角色。</t>
         </is>
       </c>
       <c r="AX5" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="BB5" s="6" t="inlineStr">
         <is>
-          <t>4.4体のS品質の水属性キャラは、他の同属性のS品質2体と組み合わせて4+2の陣形オーラを構成できる。推奨:先制のダメージを強化するための2体の神属性、または先制の制御効果の2体の氷属性キャラ。</t>
+          <t>4.4个S品质的水属性角色可以和其他2个S品质的S品质组合构成4+2的阵形气。推荐：2个神属性用于强化先发伤害，或2个冰属性角色用于先发控制效果。</t>
         </is>
       </c>
       <c r="BC5" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>制御重視</t>
+          <t>控制重点</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>制御重視</t>
+          <t>控制重点</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>制御重視</t>
+          <t>控制重点</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>様々な制御効果を応用し、敵を縛りつける編成</t>
+          <t>应用各种控制效果，束缚敌人的编成</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>制御効果</t>
+          <t>控制效果</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AH6" s="4" t="inlineStr">
         <is>
-          <t>凍結、沈黙、石化など、様々な制御効果で敵の攻撃リズムを崩す</t>
+          <t>使用冻结、沉默、石化等各种控制效果来破坏敌人的攻击节奏</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AM6" s="6" t="inlineStr">
         <is>
-          <t>1、急凍鳥と幾何雪花スキル効果は高確率の凍結効果を付与する。</t>
+          <t>1、急冻鸟和几何雪花技能效果赋予高概率的冻结效果。</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AR6" s="6" t="inlineStr">
         <is>
-          <t>2.黑夜魔靈の黒洞効果は目標を黒洞内に監禁し、攻撃することも、受けることもできなくする。</t>
+          <t>2.暗夜魔灵的黑洞效果将目标监禁在黑洞内，无法攻击或承受。</t>
         </is>
       </c>
       <c r="AS6" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AW6" s="6" t="inlineStr">
         <is>
-          <t>3.夢幻：スキルで目標を沈黙状態を付与する。</t>
+          <t>3.梦幻：用技能赋予目标沉默状态。</t>
         </is>
       </c>
       <c r="AX6" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="BB6" s="6" t="inlineStr">
         <is>
-          <t>4.胡地：目標を石化状態にできる。</t>
+          <t>4.胡地：可将目标变为石化状态。</t>
         </is>
       </c>
       <c r="BC6" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="BG6" s="6" t="inlineStr">
         <is>
-          <t>恐怖効果は制御率属性の影響を受け、同時に目標の属性を減少する。</t>
+          <t>恐怖效果受到控制率属性的影响，同时减少目标属性。</t>
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>単体攻撃</t>
+          <t>单体攻击</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>単体攻撃</t>
+          <t>单体攻击</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>単体攻撃</t>
+          <t>单体攻击</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>敵単体に対して集中的に攻撃を与え、秒殺する編成</t>
+          <t>对敌方单体集中攻击，秒杀的编成</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>単体攻撃</t>
+          <t>单体攻击</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="AH7" s="4" t="inlineStr">
         <is>
-          <t>必殺スキルは敵単体に集中させ、秒殺する</t>
+          <t>必杀技能集中于敌方单体，秒杀</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AM7" s="6" t="inlineStr">
         <is>
-          <t>1、火焰雞全体にダメージバフを付与する。</t>
+          <t>1、对火焰鸡全体给予伤害增益。</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AR7" s="6" t="inlineStr">
         <is>
-          <t>2.飛天螳螂と木守宮は協力して後列の敵を秒殺する。</t>
+          <t>2.飞天螳螂与木守宫配合秒杀后排敌人。</t>
         </is>
       </c>
       <c r="AS7" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AW7" s="6" t="inlineStr">
         <is>
-          <t>3.1体へ大ダメージを与え、敵1体を戦闘不能にする。</t>
+          <t>3.1对机体造成巨大伤害，使1个敌人无法战斗。</t>
         </is>
       </c>
       <c r="AX7" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>敵から属性やステータスを奪うことで臨機応変な戦闘に対応できる編成</t>
+          <t>通过夺取敌人的属性和状态来应对随机应变的战斗编成</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t>属性奪取</t>
+          <t>属性夺取</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="AH8" s="4" t="inlineStr">
         <is>
-          <t>奪取したステータスや属性は敵を弱くし、味方を強くする</t>
+          <t>夺取的状态和属性会使敌人变弱，伙伴变强</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AM8" s="6" t="inlineStr">
         <is>
-          <t>1、阿勃梭魯目標のHP上限を奪取する。</t>
+          <t>1、夺取阿勃梭鲁目标的HP上限。</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AR8" s="6" t="inlineStr">
         <is>
-          <t>2.三首惡龍多段攻撃はターゲットの特攻・物攻力を奪取する。</t>
+          <t>2.三首恶龙多段攻击夺取目标的特攻·物攻力。</t>
         </is>
       </c>
       <c r="AS8" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AW8" s="6" t="inlineStr">
         <is>
-          <t>3.索羅亞克：変身目標の攻撃力バフを獲得する。</t>
+          <t>3.索罗亚克：获得变身目标攻击力增益。</t>
         </is>
       </c>
       <c r="AX8" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="BB8" s="6" t="inlineStr">
         <is>
-          <t>4.黑魯加：敵全員の物理防御と魔法防御を奪い、味方全体の攻撃力と魔法攻撃力に変換する。</t>
+          <t>黑鲁加：夺取全体敌人的物理防御和魔法防御，转换为我方全体的攻击力和魔法攻击力。</t>
         </is>
       </c>
       <c r="BC8" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="BG8" s="6" t="inlineStr">
         <is>
-          <t>5.瑪狃拉：目標の物理攻撃力を奪う。</t>
+          <t>瑪狃拉：夺取目标的物理攻击力。</t>
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="BL8" s="7" t="inlineStr">
         <is>
-          <t>6.流氓鱷：目標に暗闇、治療禁止状態を付与する。</t>
+          <t>流氓鱷：赋予目标黑暗，禁止治疗状态。</t>
         </is>
       </c>
       <c r="BM8" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>様々なバフを重ねて覚醒値の回復速度を上昇させる。これにより、必殺スキルの発動間隔を短縮させ、敵に麻痺を与える。{0}のパッシブスキルにより、雷属性の味方は戦闘開始時に大量の覚醒値を獲得し、必殺スキルで一気に敵にダメージを与える。</t>
+          <t>叠加各种增益来提升觉醒值的回复速度。由此缩短必杀技能的发动间隔，对敌人造成麻痹。{0}的被动技能可以让雷属性的伙伴在战斗开始时获得大量的觉醒值，用必杀技能一口气对敌人造成伤害。</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>麻痺効果</t>
+          <t>麻痹效应</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AH9" s="7" t="inlineStr">
         <is>
-          <t>感電効果：感電目標の雷公へのダメージを減少させ、閃電鳥は感電の印のある敵へのダメージが上昇する。電龍は感電の印がある敵を攻撃する時、追加で覚醒値の回復が上昇する。</t>
+          <t>电击效果：减少电击目标雷公的伤害，电击鸟对有电击印记的敌人的伤害上升。电龙攻击有触电迹象的敌人时，会增加觉醒值回复。</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AM9" s="7" t="inlineStr">
         <is>
-          <t>1、閃電鳥、電龍は大量の感電の印を付与し、チームの覚醒値を上昇する。</t>
+          <t>1、闪电鸟、电龙给予大量的电击印记，提升队伍觉醒值。</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AR9" s="6" t="inlineStr">
         <is>
-          <t>2.雷公感電目標のダメージ減少し、目標を麻痺/スタン状態にし、フィールド制御効果を達成する。</t>
+          <t>2.雷公电击减少目标伤害，使目标进入瘫痪/昏迷状态，达到场地控制效果。</t>
         </is>
       </c>
       <c r="AS9" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AW9" s="6" t="inlineStr">
         <is>
-          <t>3.：【感電】を付与し、味方の覚醒値を回復させ、仲間全員の必殺スキル発動を加速する。</t>
+          <t>3.：赋予【触电】，回复伙伴的觉醒值，加速全体伙伴的必杀技能发动。</t>
         </is>
       </c>
       <c r="AX9" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="BB9" s="6" t="inlineStr">
         <is>
-          <t>4.电击魔兽：蓄電による攻撃が特徴の雷属性のアタッカー。</t>
+          <t>电击魔兽：以蓄电攻击为特征的雷属性攻击者。</t>
         </is>
       </c>
       <c r="BC9" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BG9" s="6" t="inlineStr">
         <is>
-          <t>5.自爆磁怪：自爆で高ダメージを与え、麻痺効果を付与する。</t>
+          <t>5.自爆磁怪：自爆造成高伤害，给予麻痹效果。</t>
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="BL9" s="6" t="inlineStr">
         <is>
-          <t>6.巨金怪：雷属性の仲間を守り、4{0}2のオーラ編成において1番の編成。</t>
+          <t>巨金怪：保护雷属性的伙伴，4{0}2的气编成中一号的编成。</t>
         </is>
       </c>
       <c r="BM9" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>反撃重視</t>
+          <t>重视反击</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>反撃重視</t>
+          <t>重视反击</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>反撃重視</t>
+          <t>重视反击</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>高い防御力で敵の攻撃を耐えつつ、強力な攻撃を与えるバランスの取れた編成</t>
+          <t>以高防御力承受敌人攻击的同时，给予强力攻击的均衡编成</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>防御と反撃重視</t>
+          <t>重视防守和反击</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AH10" s="4" t="inlineStr">
         <is>
-          <t>不死、シールド、挑発など、様々な防衛手段を駆使する</t>
+          <t>使用不死、护盾、挑衅等各种防卫手段</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AM10" s="6" t="inlineStr">
         <is>
-          <t>1.波士可朵拉はチーム全体にシールドを付与し、全体の生存率を上昇する。</t>
+          <t>1.波士可朵拉给予全队护盾，提升全队生存率。</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AR10" s="6" t="inlineStr">
         <is>
-          <t>2.超甲狂犀：自身の物理防御が高い</t>
+          <t>超甲狂犀：自身物理防御高</t>
         </is>
       </c>
       <c r="AS10" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AW10" s="6" t="inlineStr">
         <is>
-          <t>3.班基拉斯：致命ダメージを無効化し、HPが0の状態で敵を反撃して戦闘不能にする。</t>
+          <t>班基拉斯：将致命伤害无效化，在HP为0的状态下反击敌人使其无法战斗。</t>
         </is>
       </c>
       <c r="AX10" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="BB10" s="6" t="inlineStr">
         <is>
-          <t>4.巨金怪：挑発で(挑発効果中、敵は必殺スキルの攻撃のみ行える巨金怪)、味方を守る。同時に、自身の覚醒値を追加で蓄積し、必殺スキルの火力を強化する。</t>
+          <t>4.巨金怪：挑衅（挑衅效果中，敌人只能进行必杀技能攻击的巨金怪），保护我方。同时追加自身觉醒值，强化必杀技能的火力。</t>
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="BG10" s="6" t="inlineStr">
         <is>
-          <t>5.流氓鱷：範囲攻撃を行うが、範囲内の目標への攻撃が外れることがある。</t>
+          <t>流氓鱷：进行范围攻击，但对范围内目标的攻击有可能脱离。</t>
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="BL10" s="6" t="inlineStr">
         <is>
-          <t>6.巨沼怪：高い会心耐性を持ち、自身に少量のデバフ解除能力を付与する。HPが低い状態は非常に高いダメージ減少率を獲得する。</t>
+          <t>6.巨沼怪：有很高的暴击抵抗，赋予自身少量减益解除能力。生命值低的状态获得非常高的伤害减少率。</t>
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>金属性の編成</t>
+          <t>金属结构</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
-          <t>金属性の連携</t>
+          <t>金属连接</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AH11" s="4" t="inlineStr">
         <is>
-          <t>全体シールド、連携、自爆などで敵を倒す</t>
+          <t>用全体护盾、联合、自爆等打倒敌人</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM11" s="6" t="inlineStr">
         <is>
-          <t>1.波士可朵拉：チーム全体にシールドを付与する。チーム全体の生存率を上昇し、小スキルは萎縮状態を付与する。</t>
+          <t>1.波士可朵拉：给予全队护盾。提高队伍整体的生存率，小技能赋予萎缩状态。</t>
         </is>
       </c>
       <c r="AN11" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AR11" s="6" t="inlineStr">
         <is>
-          <t>2.路卡利歐：物攻·特攻、攻撃を支援し、弱点効果を強化する。</t>
+          <t>2.路卡莉欧：物攻特攻，支援攻击，强化弱点效果。</t>
         </is>
       </c>
       <c r="AS11" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AW11" s="6" t="inlineStr">
         <is>
-          <t>3.巨鉗螳螂：殺戮の印を付与し、追加攻撃を行う。攻撃を吸収し、残りHPが少ない敵を戦闘不能にする。</t>
+          <t>3.巨钳螳螂：给予杀戮之印，进行追加攻击。吸收攻击，使剩余生命值较少的敌人不能战斗。</t>
         </is>
       </c>
       <c r="AX11" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="BB11" s="6" t="inlineStr">
         <is>
-          <t>4.自爆磁怪：戦闘不能時に雷属性の大ダメージを与える。</t>
+          <t>自爆磁怪：无法战斗时造成雷属性的大伤害。</t>
         </is>
       </c>
       <c r="BC11" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="BG11" s="6" t="inlineStr">
         <is>
-          <t>5.巨金怪：味方を守りつつ、力を溜めて一気にダメージを与える。</t>
+          <t>5.巨金怪：在保护伙伴的同时，积蓄力量一口气造成伤害。</t>
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="BL11" s="6" t="inlineStr">
         <is>
-          <t>6.豎盾劍怪：攻守両立で、攻撃を支援し、前列と後列をサポートする。</t>
+          <t>6.愣头愣脑：攻守兼顾，支援攻击，支持前排和后排。</t>
         </is>
       </c>
       <c r="BM11" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>凍結制御</t>
+          <t>冻结控制</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>凍結制御</t>
+          <t>冻结控制</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>凍結制御</t>
+          <t>冻结控制</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>氷属性で凍結を敵に与え、制御する。さらに防御、攻撃力なども備えた編成</t>
+          <t>用冰属性给予敌人冻结，进行控制。更具备防御、攻击力等的编成</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>凍結と制御重視</t>
+          <t>重视冻结和控制</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>敵を凍結し制御する</t>
+          <t>冻结和控制敌人</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AM12" s="6" t="inlineStr">
         <is>
-          <t>1.雷吉艾斯：アイスコア攻撃耐性、味方の氷属性のHPを回復する。</t>
+          <t>雷吉艾斯：冰芯攻击抗性，回复我方冰属性的生命值。</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AR12" s="6" t="inlineStr">
         <is>
-          <t>2.急凍鳥と幾何雪花のスキル効果には、高確率で凍結効果を付与する。</t>
+          <t>2.急冻鸟和几何雪花的技能效果有高概率附加冻结效果。</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AW12" s="6" t="inlineStr">
         <is>
-          <t>3.瑪狃拉：氷牢で制御効果をさらに強化する。</t>
+          <t>3.瑪狃拉：用冰牢进一步强化控制效果。</t>
         </is>
       </c>
       <c r="AX12" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="BB12" s="6" t="inlineStr">
         <is>
-          <t>4.暴雪王：味方全体の凍結確率を上昇する。</t>
+          <t>暴雪王：提升我方全体冻结概率。</t>
         </is>
       </c>
       <c r="BC12" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="BG12" s="6" t="inlineStr">
         <is>
-          <t>5.冰雪龍：氷属性チームで全体のシールド強度を強化する。</t>
+          <t>5.冰雪龙：冰属性队伍增强全体护盾强度。</t>
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>神属性の編成で防御、攻撃力、支援共に備わった編成。シールド持ちの敵にも有利に戦える。</t>
+          <t>神属性的编成，防御、攻击力、支援都具备的编成。对持有护盾的敌人也能有利地战斗。</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AH13" s="4" t="inlineStr">
         <is>
-          <t>シールド持ちの敵にも有利に戦える</t>
+          <t>对持有护盾的敌人也能有利地战斗</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AM13" s="6" t="inlineStr">
         <is>
-          <t>1.黏美龍：味方の特防、自身の会心耐性が上昇する。</t>
+          <t>1.黏海龙：己方特防，提高自身暴击抵抗。</t>
         </is>
       </c>
       <c r="AN13" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AR13" s="6" t="inlineStr">
         <is>
-          <t>2.暴飛龍：裂刃ダメージ、治療禁止効果を付与し、シールドを貫通するダメージを与える。</t>
+          <t>2.暴飞龙：施加裂刃伤害，禁止治疗效果，造成穿透护盾的伤害。</t>
         </is>
       </c>
       <c r="AS13" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW13" s="6" t="inlineStr">
         <is>
-          <t>3.烈咬陸鯊：HPが少ない時、会心となる確定ダメージを与え、大ダメージを与える。</t>
+          <t>烈咬陆鲨鱼：HP少的时候，造成会心的真实伤害，造成大伤害。</t>
         </is>
       </c>
       <c r="AX13" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="BB13" s="6" t="inlineStr">
         <is>
-          <t>4.雙斧戰龍：追撃でダメージを強化し、敵を次々と戦闘不能にする。</t>
+          <t>4.双斧战龙：追击强化伤害，使敌人一个接一个无法战斗。</t>
         </is>
       </c>
       <c r="BC13" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="BG13" s="6" t="inlineStr">
         <is>
-          <t>5.快龍：デバフでダメージを上昇するアタッカー。竜属性にデバフを付与する。</t>
+          <t>5.快龙：减益使伤害上升的攻击者。对龙属性赋予减益。</t>
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="BL13" s="6" t="inlineStr">
         <is>
-          <t>6.音波龍：シールドを貫通し、仲間をサポートする。</t>
+          <t>6.声波龙：穿透护盾，支援伙伴。</t>
         </is>
       </c>
       <c r="BM13" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>制御と防御</t>
+          <t>控制和防御</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>制御と防御</t>
+          <t>控制和防御</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>制御と防御</t>
+          <t>控制和防御</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>高い防御力に敵を制御する編成。持久戦に強く、敵を封じつつ戦える。</t>
+          <t>组织控制敌人的高防御能力。擅长持久战，能封住敌人战斗。</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>防御と制御重視</t>
+          <t>重视防御和控制</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AH14" s="4" t="inlineStr">
         <is>
-          <t>防御し、反撃する。持久戦に使いやすい編成</t>
+          <t>防守和反击。易于用于持久战的组织</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AM14" s="6" t="inlineStr">
         <is>
-          <t>1.制御：急凍鳥+雪花、星8スキル解放後、急凍鳥は雪花制御率を上昇し、凍結破壊のダメージが35から55に上昇する。</t>
+          <t>1.控制：急冻鸟+雪花，8星技能释放后，急冻鸟提高雪花控制率，冰冻破坏的伤害从35提高到55。</t>
         </is>
       </c>
       <c r="AN14" s="2" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AR14" s="6" t="inlineStr">
         <is>
-          <t>2.アタッカー：瑪狃拉、敵が凍結状態である場合、ダメージが最大になる。</t>
+          <t>攻击者：瑪狃拉，敌人处于冻结状态时，伤害最大。</t>
         </is>
       </c>
       <c r="AS14" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AW14" s="6" t="inlineStr">
         <is>
-          <t>3.劍盾：味方のダメージを肩代わりし、味方と共に攻撃することができる。</t>
+          <t>3.剑盾：可以承担伙伴的伤害，和伙伴一起攻击。</t>
         </is>
       </c>
       <c r="AX14" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="BB14" s="6" t="inlineStr">
         <is>
-          <t>4.洛奇亞味方を守り、自身は致命ダメージを無効化。耐久力を強化する。</t>
+          <t>4.洛奇亚保护我方，自身致命伤害无效化。加强耐力。</t>
         </is>
       </c>
       <c r="BC14" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="BG14" s="6" t="inlineStr">
         <is>
-          <t>5.ランクスキル解放後、氷属性の全体制御力が上昇する。雪花と可哥を主力に据え、急凍鳥で制御力を強化し、狃拉でダメージを与える編成がおすすめ。洛奇亞は他の空属性キャラに置き換えても代用できる。</t>
+          <t>5.等级技能解放后，冰属性全体控制力上升。推荐以雪花和可哥为主力，使用急冻鸟强化控制力，使用狃拉给予伤害的编成。洛奇亚也可以替换成其他空属性角色来代替。</t>
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>連携重視</t>
+          <t>重视合作</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>連携重視</t>
+          <t>重视合作</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>連携重視</t>
+          <t>重视合作</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>味方の連携スキルで瞬時に敵を倒せる編成</t>
+          <t>能利用我方的联合技能瞬间打倒敌人的组合</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>連携重視</t>
+          <t>重视合作</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="AH15" s="4" t="inlineStr">
         <is>
-          <t>仲間の連携で敵を瞬時に倒す</t>
+          <t>通过伙伴的合作瞬间打倒敌人</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AR15" s="6" t="inlineStr">
         <is>
-          <t>2.水君を前列に配置する理由は、加速オーラの効果で、先に敵を撃破する。</t>
+          <t>2.将水君配置在前排的理由是，利用加速气的效果，先击破敌人。</t>
         </is>
       </c>
       <c r="AS15" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AW15" s="6" t="inlineStr">
         <is>
-          <t>3.火焰雞：パッシブオーラで仲間全員のダメージ量が上昇する。</t>
+          <t>3.火焰鸡：被动气使全体伙伴的伤害量上升。</t>
         </is>
       </c>
       <c r="AX15" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="BB15" s="6" t="inlineStr">
         <is>
-          <t>4.劍怪：スキル更新後、この編成に最適化。自身の攻撃力と防御力を強化し、スキルで後列の攻撃力を20%上昇、前列の耐久力を上昇。スキルで全員の速度を上昇する。</t>
+          <t>4.剑怪：技能更新后，最适合这个编成。强化自身的攻击力和防御力，技能使后排攻击力上升20%，前排耐力上升。技能提升所有人的速度。</t>
         </is>
       </c>
       <c r="BC15" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="BG15" s="6" t="inlineStr">
         <is>
-          <t>5.巨鉗螳螂：パッシブで敵を倒すと追加攻撃を発動し、堅盾の効果や火雞のパッシブと組み合わせで敵をに大ダメージを与える。</t>
+          <t>巨钳螳螂：用被动招式打倒敌人后发动追加攻击，配合坚盾效果和火鸡的被动招式对敌人造成较大伤害。</t>
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>自爆編成</t>
+          <t>自爆编组</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>自爆編成</t>
+          <t>自爆编组</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>自爆編成</t>
+          <t>自爆编组</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>通常の戦闘ではあまり役には立たないが、編成次第では強力な破壊力を持ち合わせており、一撃特化の編成</t>
+          <t>虽然在一般的战斗中没什么用处，但根据编成的不同，拥有强大的破坏力，一击特化的编成</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>自爆編成</t>
+          <t>自爆编组</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AH16" s="4" t="inlineStr">
         <is>
-          <t>自爆で敵を瞬時に倒す</t>
+          <t>用自爆瞬间打倒敌人</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AM16" s="6" t="inlineStr">
         <is>
-          <t>1.自爆磁怪，隆隆岩，瓦斯彈戦闘不能時に高い自爆ダメージを与える。</t>
+          <t>1.自爆磁怪，隆隆岩，瓦斯弹无法战斗时造成高自爆伤害。</t>
         </is>
       </c>
       <c r="AN16" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="AR16" s="6" t="inlineStr">
         <is>
-          <t>2.爆音怪は敵味方を問わず攻撃を発動する。</t>
+          <t>2.爆音怪不分敌我发动攻击。</t>
         </is>
       </c>
       <c r="AS16" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="AW16" s="6" t="inlineStr">
         <is>
-          <t>3.味方が戦闘不能になると、火炎獅のダメージ量が上昇する</t>
+          <t>3.我方无法战斗时，火焰狮的伤害量上升</t>
         </is>
       </c>
       <c r="AX16" s="2" t="inlineStr">
